--- a/site/Integration-Schedule-Setup-Guide/headings.xlsx
+++ b/site/Integration-Schedule-Setup-Guide/headings.xlsx
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Weekly Schedule Setup in V5 Version of User Integration and Script Integration</t>
+          <t>Weekly Schedule Setup from V5 Version Onwards</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
